--- a/job_application_forms/045_event_production_internship_application_form--job_application_forms.xlsx
+++ b/job_application_forms/045_event_production_internship_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25-30</t>
+          <t>30-35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>25-30</t>
+          <t>30-35</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-35</t>
+          <t>35-40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>30-35</t>
+          <t>35-40</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>35-40</t>
+          <t>below_20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>35-40</t>
+          <t>Below 20</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>below_20</t>
+          <t>40-45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Below 20</t>
+          <t>40-45</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>40-45</t>
+          <t>45-50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>40-45</t>
+          <t>45-50</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>salary_range_choices</t>
+          <t>notice_period_unit_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>45-50</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45-50</t>
+          <t>Hour</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>half_day</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>Half Day</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>half_day</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Half Day</t>
+          <t>Day</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>notice_period_unit_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>family_member</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Family Member</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>coworker</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Coworker</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>coworker</t>
+          <t>photography</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Coworker</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>photography</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Photography</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>graphic_design</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Writing</t>
+          <t>Graphic Design</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>graphic_design</t>
+          <t>social_media_management</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Graphic Design</t>
+          <t>Social Media Management</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>social_media_management</t>
+          <t>event_planning</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Social Media Management</t>
+          <t>Event Planning</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>event_planning</t>
+          <t>video_production</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Event Planning</t>
+          <t>Video Production</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>video_production</t>
+          <t>music_production</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Video Production</t>
+          <t>Music Production</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1811,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>music_production</t>
+          <t>audio_production</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Music Production</t>
+          <t>Audio Production</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>languages_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>audio_production</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Audio Production</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
@@ -1913,29 +1913,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>italian</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italian</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>languages_choices</t>
+          <t>references_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1947,29 +1947,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>references_choices</t>
+          <t>availability_period_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>short-term</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Short-term</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>short-term</t>
+          <t>long-term</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>Long-term</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>availability_period_choices</t>
+          <t>work_experience_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>long-term</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long-term</t>
+          <t>Intern</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>intern</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -2032,27 +2032,10 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>freelance</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>work_experience_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>part-time</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
